--- a/data/trans_orig/IP36BS1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP36BS1-Edad-trans_orig.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -7204,12 +7204,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7952,12 +7952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -8938,12 +8938,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -9246,12 +9246,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9316,12 +9316,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>64,98%</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -9811,12 +9811,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9896,12 +9896,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -9924,12 +9924,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -10267,12 +10267,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>41862</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -10719,12 +10719,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10754,12 +10754,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -10832,12 +10832,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -10945,12 +10945,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11535,12 +11535,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -12433,7 +12433,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -12541,12 +12541,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12556,12 +12556,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -13028,12 +13028,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13269,12 +13269,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13289,12 +13289,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13304,12 +13304,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,07%</t>
         </is>
       </c>
     </row>
@@ -13489,7 +13489,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -13562,12 +13562,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13632,12 +13632,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -14014,12 +14014,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14084,12 +14084,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14099,12 +14099,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14162,12 +14162,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -14240,12 +14240,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14255,12 +14255,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -14583,12 +14583,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14598,12 +14598,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14618,12 +14618,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14633,12 +14633,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14653,12 +14653,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14668,12 +14668,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -15035,12 +15035,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15050,12 +15050,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -15183,12 +15183,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -15296,12 +15296,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15346,12 +15346,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -15604,12 +15604,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15619,12 +15619,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16091,12 +16091,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16106,12 +16106,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16141,12 +16141,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -16169,12 +16169,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16184,12 +16184,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16219,12 +16219,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16254,12 +16254,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -16282,12 +16282,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16297,12 +16297,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16317,12 +16317,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>31113</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16367,12 +16367,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -17384,7 +17384,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -17492,12 +17492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -17507,12 +17507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -17610,7 +17610,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -17883,7 +17883,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -17898,7 +17898,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -17948,12 +17948,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -17963,12 +17963,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -18026,12 +18026,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -18041,12 +18041,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -18061,12 +18061,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -18076,12 +18076,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -18252,12 +18252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -18267,12 +18267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -18287,12 +18287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -18302,12 +18302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -18345,12 +18345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -18365,12 +18365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -18380,12 +18380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -18400,12 +18400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -18415,12 +18415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -18448,7 +18448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -18513,12 +18513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -18528,12 +18528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -18919,7 +18919,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -19012,12 +19012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -19027,12 +19027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -19047,12 +19047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -19062,12 +19062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -19082,12 +19082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -19097,12 +19097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -19351,12 +19351,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -19366,12 +19366,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -19421,12 +19421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -19436,12 +19436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -19464,12 +19464,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -19479,12 +19479,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -19534,12 +19534,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -19549,12 +19549,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -19577,12 +19577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -19592,12 +19592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -19617,7 +19617,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -19632,7 +19632,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -19647,12 +19647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -19662,12 +19662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -19935,12 +19935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -19990,12 +19990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -20005,12 +20005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -20053,7 +20053,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -20068,12 +20068,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -20083,12 +20083,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -20103,12 +20103,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -20118,12 +20118,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -20334,7 +20334,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -20349,7 +20349,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -20372,12 +20372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -20407,12 +20407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -20422,12 +20422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -20442,12 +20442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -20457,12 +20457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -20485,12 +20485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -20500,12 +20500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -20520,12 +20520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>419</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -20535,12 +20535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20555,12 +20555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -20570,12 +20570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -20598,12 +20598,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -20613,12 +20613,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -20633,12 +20633,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>921</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -20648,12 +20648,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -20668,12 +20668,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -20683,12 +20683,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -20941,12 +20941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -20956,12 +20956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>394</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20991,12 +20991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -21026,12 +21026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -21069,12 +21069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -21089,12 +21089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -21104,12 +21104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -21124,12 +21124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -21139,12 +21139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -21315,12 +21315,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -21330,12 +21330,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -21350,12 +21350,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -21365,12 +21365,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -21393,12 +21393,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -21408,12 +21408,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -21428,12 +21428,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -21443,12 +21443,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21463,12 +21463,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -21478,12 +21478,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -21506,12 +21506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -21521,12 +21521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -21556,12 +21556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21576,12 +21576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -21591,12 +21591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -21619,12 +21619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -21634,12 +21634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21654,12 +21654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -21669,12 +21669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21689,12 +21689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -21704,12 +21704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
